--- a/Lab3/checklist_lab3.xlsx
+++ b/Lab3/checklist_lab3.xlsx
@@ -171,7 +171,7 @@
     <t>2. Hardware Simulation (Verilog): The Verilog testbench reads the input .txt file, runs the FSM-based simulation case-by-case (executing a clean hardware reset before each independent case), and dumps the raw hardware outputs into a text file.</t>
   </si>
   <si>
-    <t>3. Automated Verification (Python): A Python script reads the dumped hardware output file, matches the results against an algorithmic golden model, and automatically checks for accuracy while safely handling any shuffled root ordering.</t>
+    <t>3. Automated Verification (Python): A Python script reads the dumped hardware output file, matches the results against an algorithmic golden model, and automatically checks for accuracy while safely handling any shuffled root ordering. Condition PASS:  |(output - expected)/expected| &lt; 0.1% (if expected = 0 then use |output| &lt; 0.1%)</t>
   </si>
 </sst>
 </file>
@@ -2269,8 +2269,6 @@
     <row r="985" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="J18:J21"/>
-    <mergeCell ref="K18:K21"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="H8:H9"/>
@@ -2278,21 +2276,23 @@
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="L8:L9"/>
-    <mergeCell ref="J13:J17"/>
     <mergeCell ref="K13:K17"/>
     <mergeCell ref="L13:L17"/>
+    <mergeCell ref="D18:D21"/>
     <mergeCell ref="E18:E21"/>
     <mergeCell ref="H13:H17"/>
     <mergeCell ref="H18:H21"/>
+    <mergeCell ref="I18:I21"/>
+    <mergeCell ref="J18:J21"/>
+    <mergeCell ref="K18:K21"/>
+    <mergeCell ref="L18:L21"/>
+    <mergeCell ref="B13:B21"/>
+    <mergeCell ref="C13:C21"/>
+    <mergeCell ref="D13:D17"/>
     <mergeCell ref="E13:E17"/>
     <mergeCell ref="I13:I17"/>
-    <mergeCell ref="D13:D17"/>
-    <mergeCell ref="B13:B21"/>
-    <mergeCell ref="C13:C21"/>
-    <mergeCell ref="D18:D21"/>
+    <mergeCell ref="J13:J17"/>
     <mergeCell ref="F18:F21"/>
-    <mergeCell ref="I18:I21"/>
-    <mergeCell ref="L18:L21"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
